--- a/InoueNakamura__1997/InoueNakamura__1997_registry_rows.xlsx
+++ b/InoueNakamura__1997/InoueNakamura__1997_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R37722837afa74fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R7d33a78471e64725"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rddfc8793ada947e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R3cfde140f1d34b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R606abe80277a4f59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R10ec23493abf428f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Behavioural responses to mirrors across 12 primate species</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Results / figures / tables: item selection pending</x:v>
+        <x:v>Table 3: Summary of responses to mirror image in primates</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap
@@ -350,13 +350,13 @@
         <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 7 / printed p. 272. Mixed present-study and literature evidence: preserve asterisks, bold species and references. Circles = positive; crosses = negative; dashes = unavailable. These behavioural categories are not equivalent to standard mark-test pass/fail. Figures 1–3 contain present-study behavioural-duration results; Tables 1–2 provide subjects and definitions.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/1960709854/Inoue-Nakamura-1997-Mirror Self-recognition in.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -514,7 +514,9 @@
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Table 3</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: InoueNakamura__1997. Target: Results / figures / tables: item selection pending. Candidate broad comparative source. Verify original species/sample list and behaviour categories in full text. Mirror-interest or self-directed behaviour categories must not automatically become standard mark-test successes.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote correction 2026-10-25: Verified in EndNote full text — PDF p. 7 / printed p. 272. Mixed present-study and literature evidence: preserve asterisks, bold species and references. Circles = positive; crosses = negative; dashes = unavailable. These behavioural categories are not equivalent to standard mark-test pass/fail. Figures 1–3 contain present-study behavioural-duration results; Tables 1–2 provide subjects and definitions. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/1960709854/Inoue-Nakamura-1997-Mirror Self-recognition in.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
@@ -563,7 +565,7 @@
       <x:c r="AC2" s="3"/>
       <x:c r="AD2" s="3"/>
       <x:c r="AE2" s="3" t="str">
-        <x:v>primary</x:v>
+        <x:v>both</x:v>
       </x:c>
       <x:c r="AF2" s="3"/>
       <x:c r="AG2" s="3" t="str">
@@ -711,7 +713,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>Blank Item number means full text is still required or the source is REFERENCE ONLY. The six EndNote PDFs identified on 2026-10-25 are linked in Source list and their source-folder notes. Smaers 2013 Table 1 is now verified. Human snapshot checks remain pending.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -995,13 +997,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3544343A-2525-43B1-9FA1-E480854C4512}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94921616-0555-42B5-A176-DFD8B90362DD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B650EF-4DF2-4809-8E8C-7EEE86C5FCB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9415DF4B-0460-4F48-87B4-F4731BF5A9D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9F5C098-9023-407D-89D0-B87959F36A25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0999EE2-6DE6-4BFC-9BBC-4FE9A6050D05}"/>
 </file>